--- a/AQI Predictor/Models/Model Evaluation.xlsx
+++ b/AQI Predictor/Models/Model Evaluation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sameen\10 Pearls Project\AQI Predictor\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4294E235-38BF-4311-BCBC-79EE5E8F36A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE46E7B6-B987-465A-BE01-CCA9A5D2FD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Models</t>
   </si>
@@ -61,13 +61,55 @@
   </si>
   <si>
     <t>XG-Boost</t>
+  </si>
+  <si>
+    <t>CatBoost Day 1 (Hourly)</t>
+  </si>
+  <si>
+    <t>CatBoost Day 2 (Hourly)</t>
+  </si>
+  <si>
+    <t>CatBoost Day 3 (Hourly)</t>
+  </si>
+  <si>
+    <t>CatBoost Day 1 (Daily)</t>
+  </si>
+  <si>
+    <t>CatBoost</t>
+  </si>
+  <si>
+    <t>CatBoost Day 2 (Daily)</t>
+  </si>
+  <si>
+    <t>CatBoost Day 3 (Daily)</t>
+  </si>
+  <si>
+    <t>FaceBook Prophet</t>
+  </si>
+  <si>
+    <t>Prophet Day 1 (Hourly)</t>
+  </si>
+  <si>
+    <t>Prophet Day 2 (Hourly)</t>
+  </si>
+  <si>
+    <t>Prophet Day 3 (Hourly)</t>
+  </si>
+  <si>
+    <t>Prophet Day 3 (Daily)</t>
+  </si>
+  <si>
+    <t>Prophet Day 1 (Daily)</t>
+  </si>
+  <si>
+    <t>Prophet Day 2 (Daily)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,8 +125,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -93,19 +151,25 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -113,24 +177,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Output" xfId="1" builtinId="21"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -146,8 +233,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5FB12A2D-E164-4F33-B656-6A581DB1D701}" name="Table2" displayName="Table2" ref="A1:E8" totalsRowShown="0">
-  <autoFilter ref="A1:E8" xr:uid="{5FB12A2D-E164-4F33-B656-6A581DB1D701}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5FB12A2D-E164-4F33-B656-6A581DB1D701}" name="Table2" displayName="Table2" ref="A1:E22" totalsRowShown="0">
+  <autoFilter ref="A1:E22" xr:uid="{5FB12A2D-E164-4F33-B656-6A581DB1D701}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{50DB6181-23F8-416D-A2FA-6FC16E42E284}" name="Models"/>
     <tableColumn id="2" xr3:uid="{01E1A0CE-6490-47B2-8078-34C426DB9933}" name="R2-Score"/>
@@ -422,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.5546875" customWidth="1"/>
@@ -450,7 +537,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="3"/>
@@ -459,105 +546,207 @@
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>0.625</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>8.5380000000000003</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>150.76300000000001</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>12.278</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>0.34899999999999998</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>11.754</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>261.56099999999998</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>16.172000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>0.29199999999999998</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>12.259</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>284.17700000000002</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>16.856999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>0.83599999999999997</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>5.3689999999999998</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>58.323999999999998</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>7.6369999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>0.55500000000000005</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>9.1080000000000005</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>159.79</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>12.64</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>0.503</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>9.8409999999999993</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>179.46199999999999</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>13.396000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="C10" s="2">
+        <v>9.0869999999999997</v>
+      </c>
+      <c r="D10" s="2">
+        <v>165.93199999999999</v>
+      </c>
+      <c r="E10" s="2">
+        <v>12.881</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.84</v>
+      </c>
+      <c r="C13" s="2">
+        <v>5.383</v>
+      </c>
+      <c r="D13" s="2">
+        <v>57.09</v>
+      </c>
+      <c r="E13" s="2">
+        <v>7.5549999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/AQI Predictor/Models/Model Evaluation.xlsx
+++ b/AQI Predictor/Models/Model Evaluation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sameen\10 Pearls Project\AQI Predictor\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE46E7B6-B987-465A-BE01-CCA9A5D2FD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392E2CF0-0FD3-459D-9BDF-54D0D526042B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -677,10 +677,34 @@
       <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="B11" s="2">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="C11" s="2">
+        <v>11.385999999999999</v>
+      </c>
+      <c r="D11" s="2">
+        <v>248.69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>15.769</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="C12" s="2">
+        <v>11.869</v>
+      </c>
+      <c r="D12" s="2">
+        <v>268.83800000000002</v>
+      </c>
+      <c r="E12" s="2">
+        <v>16.396000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">

--- a/AQI Predictor/Models/Model Evaluation.xlsx
+++ b/AQI Predictor/Models/Model Evaluation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sameen\10 Pearls Project\AQI Predictor\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392E2CF0-0FD3-459D-9BDF-54D0D526042B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E30AF73-AB45-477E-877B-ECAFF64BEFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Models</t>
   </si>
@@ -87,22 +87,13 @@
     <t>FaceBook Prophet</t>
   </si>
   <si>
-    <t>Prophet Day 1 (Hourly)</t>
-  </si>
-  <si>
-    <t>Prophet Day 2 (Hourly)</t>
-  </si>
-  <si>
-    <t>Prophet Day 3 (Hourly)</t>
-  </si>
-  <si>
-    <t>Prophet Day 3 (Daily)</t>
-  </si>
-  <si>
-    <t>Prophet Day 1 (Daily)</t>
-  </si>
-  <si>
-    <t>Prophet Day 2 (Daily)</t>
+    <t>Prophet Day 1-Regressor (Daily)</t>
+  </si>
+  <si>
+    <t>LSTM</t>
+  </si>
+  <si>
+    <t>LSTM Day 1 (Hourly)</t>
   </si>
 </sst>
 </file>
@@ -233,8 +224,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5FB12A2D-E164-4F33-B656-6A581DB1D701}" name="Table2" displayName="Table2" ref="A1:E22" totalsRowShown="0">
-  <autoFilter ref="A1:E22" xr:uid="{5FB12A2D-E164-4F33-B656-6A581DB1D701}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5FB12A2D-E164-4F33-B656-6A581DB1D701}" name="Table2" displayName="Table2" ref="A1:E20" totalsRowShown="0">
+  <autoFilter ref="A1:E20" xr:uid="{5FB12A2D-E164-4F33-B656-6A581DB1D701}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{50DB6181-23F8-416D-A2FA-6FC16E42E284}" name="Models"/>
     <tableColumn id="2" xr3:uid="{01E1A0CE-6490-47B2-8078-34C426DB9933}" name="R2-Score"/>
@@ -509,10 +500,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="34.5546875" customWidth="1"/>
     <col min="4" max="4" width="36.6640625" customWidth="1"/>
@@ -728,10 +719,34 @@
       <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="B14" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="C14" s="2">
+        <v>9.32</v>
+      </c>
+      <c r="D14" s="2">
+        <v>163.374</v>
+      </c>
+      <c r="E14" s="2">
+        <v>12.78</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>18</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.504</v>
+      </c>
+      <c r="C15" s="2">
+        <v>9.86</v>
+      </c>
+      <c r="D15" s="2">
+        <v>179.107</v>
+      </c>
+      <c r="E15" s="2">
+        <v>13.382999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -743,34 +758,61 @@
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="C17" s="2">
+        <v>9.82</v>
+      </c>
+      <c r="D17" s="2">
+        <v>172.59700000000001</v>
+      </c>
+      <c r="E17" s="2">
+        <v>13.13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C18" s="2">
+        <v>15.436</v>
+      </c>
+      <c r="D18" s="2">
+        <v>356.673</v>
+      </c>
+      <c r="E18" s="2">
+        <v>18.885000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
-        <v>23</v>
+      <c r="B20" s="2">
+        <v>0.59</v>
+      </c>
+      <c r="C20" s="2">
+        <v>9.0960000000000001</v>
+      </c>
+      <c r="E20" s="2">
+        <v>12.837999999999999</v>
       </c>
     </row>
   </sheetData>
